--- a/evaluations/response_time_increasing_clients/2_DB/aggregated_workload.xlsx
+++ b/evaluations/response_time_increasing_clients/2_DB/aggregated_workload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\evaluations\response_time_increasing_clients\2_DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96919A0-DF48-450D-BA44-4E6D29837058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB3DFA7-C853-405B-AB8E-8D2ECA2408D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>User Count</t>
   </si>
@@ -46,12 +46,15 @@
   <si>
     <t>Growth Rate Response Time</t>
   </si>
+  <si>
+    <t>Linear Growth Rate</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +66,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -72,16 +76,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,19 +121,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -416,14 +451,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,8 +472,11 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -451,8 +490,12 @@
         <f>C3/C2</f>
         <v>2.2491142211017463</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f t="shared" ref="F2:F49" si="0">C3-C2</f>
+        <v>9.6531879574803909</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -463,11 +506,15 @@
         <v>17.38121458179187</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E51" si="0">C4/C3</f>
+        <f t="shared" ref="E3:E50" si="1">C4/C3</f>
         <v>1.251432355127589</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>4.3701997172779201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -478,11 +525,15 @@
         <v>21.75141429906979</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3250660472620761</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>7.0706462685584199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -493,11 +544,15 @@
         <v>28.82206056762821</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2047677833198505</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>5.9018294531437014</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -508,11 +563,15 @@
         <v>34.723890020771911</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2154619527327422</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>7.4816771503524961</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -523,11 +582,15 @@
         <v>42.205567171124407</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.177608534463656</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>7.4960689314707949</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -538,11 +601,15 @@
         <v>49.701636102595202</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.110973279840183</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>5.5155535717282405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -553,11 +620,15 @@
         <v>55.217189674323443</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1062698681243279</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>5.8679234648863599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -568,11 +639,15 @@
         <v>61.085113139209803</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1028395685543837</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>6.2819666803320544</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -583,11 +658,15 @@
         <v>67.367079819541857</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1210280384117135</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>8.1533055240844874</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -598,11 +677,15 @@
         <v>75.520385343626344</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0842378100708125</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>6.3616718770509664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -613,11 +696,15 @@
         <v>81.882057220677311</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0783071375076496</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>6.4119495141888052</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -628,11 +715,15 @@
         <v>88.294006734866116</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0780614116020537</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>6.8923548017248919</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -643,11 +734,15 @@
         <v>95.186361536591008</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0748232427080076</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>7.1221522317444936</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -658,11 +753,15 @@
         <v>102.3085137683355</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.064080623039062</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>6.5559933044753933</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -673,11 +772,15 @@
         <v>108.86450707281089</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0596121880121938</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>6.4896514634792055</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -688,11 +791,15 @@
         <v>115.3541585362901</v>
       </c>
       <c r="E18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0598859711192947</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>6.908095806594801</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -703,11 +810,15 @@
         <v>122.2622543428849</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0598836854553439</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>7.3215143821305873</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -718,11 +829,15 @@
         <v>129.58376872501549</v>
       </c>
       <c r="E20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0476422567747841</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>6.1736631834414197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -733,11 +848,15 @@
         <v>135.75743190845691</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0517734024151206</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>7.0286241530398854</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -748,11 +867,15 @@
         <v>142.78605606149679</v>
       </c>
       <c r="E22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0481694034700584</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>6.8779191443246077</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -763,11 +886,15 @@
         <v>149.6639752058214</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0463446476556237</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>6.9361241976538111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -778,11 +905,15 @@
         <v>156.60009940347521</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.044828753546555</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>7.0201872615243985</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -793,11 +924,15 @@
         <v>163.62028666499961</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0409767540797212</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>6.704628249125193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -808,11 +943,15 @@
         <v>170.3249149141248</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0433842938309783</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>7.389426155370785</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -823,11 +962,15 @@
         <v>177.71434106949559</v>
       </c>
       <c r="E27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.041056017213456</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>7.2962430460272003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -838,11 +981,15 @@
         <v>185.01058411552279</v>
       </c>
       <c r="E28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0343108472110527</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>6.3478698840153243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -853,11 +1000,15 @@
         <v>191.35845399953811</v>
       </c>
       <c r="E29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0367272480880654</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>7.0280694137896944</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -868,11 +1019,15 @@
         <v>198.38652341332781</v>
       </c>
       <c r="E30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0334592490705832</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>6.6378640991335942</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -883,11 +1038,15 @@
         <v>205.0243875124614</v>
       </c>
       <c r="E31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0345873058882094</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>7.0912412054362903</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -898,11 +1057,15 @@
         <v>212.11562871789769</v>
       </c>
       <c r="E32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0325595193222845</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>6.9063829117989144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -913,11 +1076,15 @@
         <v>219.02201162969661</v>
       </c>
       <c r="E33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0312456068798903</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>6.8434756734242796</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -928,11 +1095,15 @@
         <v>225.86548730312089</v>
       </c>
       <c r="E34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0237864278324016</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>5.3725331135659076</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -943,11 +1114,15 @@
         <v>231.23802041668679</v>
       </c>
       <c r="E35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0253354492552014</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>5.8585191321402021</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -958,11 +1133,15 @@
         <v>237.096539548827</v>
       </c>
       <c r="E36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0319715914878915</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>7.5803537056478092</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -973,11 +1152,15 @@
         <v>244.67689325447481</v>
       </c>
       <c r="E37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0321474610921726</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>7.865740906051883</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -988,11 +1171,15 @@
         <v>252.54263416052669</v>
       </c>
       <c r="E38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0252511166176641</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>6.3769835061195295</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1003,11 +1190,15 @@
         <v>258.91961766664622</v>
       </c>
       <c r="E39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0193687587322169</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>5.0149516056230823</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1018,11 +1209,15 @@
         <v>263.9345692722693</v>
       </c>
       <c r="E40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0252878416576883</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>6.6743355957473227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1033,11 +1228,15 @@
         <v>270.60890486801662</v>
       </c>
       <c r="E41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0260906062009443</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>7.0603503713801956</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1048,11 +1247,15 @@
         <v>277.66925523939682</v>
       </c>
       <c r="E42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.023992824650042</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>6.6620697516665928</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1063,11 +1266,15 @@
         <v>284.33132499106341</v>
       </c>
       <c r="E43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0265792739946498</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>7.5573201921993132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1078,11 +1285,15 @@
         <v>291.88864518326272</v>
       </c>
       <c r="E44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0240879231964544</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>7.0309912670915651</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1093,11 +1304,15 @@
         <v>298.91963645035429</v>
       </c>
       <c r="E45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0217754418126528</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>6.5091071501840361</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1108,11 +1323,15 @@
         <v>305.42874360053833</v>
       </c>
       <c r="E46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0233218581025982</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>7.1231658187065818</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1123,11 +1342,15 @@
         <v>312.55190941924491</v>
       </c>
       <c r="E47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0202720471498168</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>6.3360670445122196</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1138,11 +1361,15 @@
         <v>318.88797646375713</v>
       </c>
       <c r="E48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0182701108582632</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>5.8261186813600716</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1153,11 +1380,15 @@
         <v>324.7140951451172</v>
       </c>
       <c r="E49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0172324345995634</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>5.5956144081446269</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1168,11 +1399,11 @@
         <v>330.30970955326183</v>
       </c>
       <c r="E50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1014148607638861</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1182,15 +1413,15 @@
       <c r="C51">
         <v>363.80802275656549</v>
       </c>
-      <c r="E51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="2">
-        <f>SUM(E2:E50)/49</f>
-        <v>1.0913613275898606</v>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F55" s="3">
+        <f>SUM(F2:F49)/48</f>
+        <v>6.7204517276864655</v>
       </c>
     </row>
   </sheetData>
